--- a/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487845_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Segunda FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487845_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>4.625</v>
+        <v>4.9637</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1008</v>
+        <v>5.4689</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.4758</v>
+        <v>-0.5052</v>
       </c>
       <c r="G2" t="n">
         <v>1.1427</v>
@@ -610,13 +610,13 @@
         <v>1.4568</v>
       </c>
       <c r="S2" t="n">
-        <v>0.1233</v>
+        <v>0.4621</v>
       </c>
       <c r="T2" t="n">
-        <v>-0.1214</v>
+        <v>0.2467</v>
       </c>
       <c r="U2" t="n">
-        <v>0.2447</v>
+        <v>0.2153</v>
       </c>
       <c r="V2" t="n">
         <v>5.0239</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.3839</v>
+        <v>1.9355</v>
       </c>
       <c r="E3" t="n">
-        <v>0.6137</v>
+        <v>1.5177</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7702</v>
+        <v>0.4179</v>
       </c>
       <c r="G3" t="n">
         <v>0.0469</v>
@@ -688,13 +688,13 @@
         <v>2.0812</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.5173</v>
+        <v>0.0343</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3049</v>
+        <v>-0.401</v>
       </c>
       <c r="U3" t="n">
-        <v>0.7875</v>
+        <v>0.4352</v>
       </c>
       <c r="V3" t="n">
         <v>0.8137</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>K. NAVARRO ARRUE</t>
+          <t>J. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.0614</v>
+        <v>-0.8561</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0269</v>
+        <v>-0.3663</v>
       </c>
       <c r="F4" t="n">
-        <v>-1.0345</v>
+        <v>-0.4898</v>
       </c>
       <c r="G4" t="n">
-        <v>-0.4515</v>
+        <v>-1.434</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.3454</v>
+        <v>-0.1131</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.1061</v>
+        <v>-1.321</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0384</v>
+        <v>0.3624</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0384</v>
+        <v>1.0465</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.6842</v>
       </c>
       <c r="M4" t="n">
-        <v>-0.4899</v>
+        <v>-1.7964</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.3838</v>
+        <v>-1.1596</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.1061</v>
+        <v>-0.6368</v>
       </c>
       <c r="P4" t="n">
-        <v>0</v>
+        <v>-0.6244</v>
       </c>
       <c r="Q4" t="n">
-        <v>0</v>
+        <v>-1.0406</v>
       </c>
       <c r="R4" t="n">
-        <v>0</v>
+        <v>0.4162</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.0261</v>
+        <v>0.4947</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.06519999999999999</v>
+        <v>0.312</v>
       </c>
       <c r="U4" t="n">
-        <v>0.0391</v>
+        <v>0.1827</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.5838</v>
+        <v>0.7076</v>
       </c>
       <c r="W4" t="n">
         <v>0</v>
       </c>
       <c r="X4" t="n">
-        <v>-0.5838</v>
+        <v>0.7076</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>J. MARIN ORTEGA</t>
+          <t>K. NAVARRO ARRUE</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.2405</v>
+        <v>-0.8955</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.6039</v>
+        <v>0.0803</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.6366000000000001</v>
+        <v>-0.9758</v>
       </c>
       <c r="G5" t="n">
-        <v>-1.434</v>
+        <v>-0.4515</v>
       </c>
       <c r="H5" t="n">
-        <v>-0.1131</v>
+        <v>-0.3454</v>
       </c>
       <c r="I5" t="n">
-        <v>-1.321</v>
+        <v>-0.1061</v>
       </c>
       <c r="J5" t="n">
-        <v>0.3624</v>
+        <v>0.0384</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0465</v>
+        <v>0.0384</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.6842</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-1.7964</v>
+        <v>-0.4899</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.1596</v>
+        <v>-0.3838</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.6368</v>
+        <v>-0.1061</v>
       </c>
       <c r="P5" t="n">
-        <v>-0.6244</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>0.4162</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>0.1103</v>
+        <v>0.1398</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0743</v>
+        <v>0.0419</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0359</v>
+        <v>0.0979</v>
       </c>
       <c r="V5" t="n">
-        <v>0.7076</v>
+        <v>-0.5838</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>0.7076</v>
+        <v>-0.5838</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.3569</v>
+        <v>-1.1868</v>
       </c>
       <c r="E6" t="n">
-        <v>-1.2967</v>
+        <v>-1.2734</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.0602</v>
+        <v>0.0866</v>
       </c>
       <c r="G6" t="n">
         <v>-0.9611</v>
@@ -922,13 +922,13 @@
         <v>1.6649</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.4365</v>
+        <v>-0.2663</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.3948</v>
+        <v>-0.3714</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.0417</v>
+        <v>0.1051</v>
       </c>
       <c r="V6" t="n">
         <v>-0.5838</v>
@@ -943,7 +943,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Z. WILLIAMS</t>
+          <t>G. FERNANDEZ DIAZ</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -955,67 +955,67 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3934</v>
+        <v>-1.7303</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.4593</v>
+        <v>-1.1705</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.9341</v>
+        <v>-0.5598</v>
       </c>
       <c r="G7" t="n">
-        <v>0.1901</v>
+        <v>-2.2669</v>
       </c>
       <c r="H7" t="n">
-        <v>-1.2068</v>
+        <v>-1.2366</v>
       </c>
       <c r="I7" t="n">
-        <v>1.3969</v>
+        <v>-1.0303</v>
       </c>
       <c r="J7" t="n">
-        <v>0.1087</v>
+        <v>-1.332</v>
       </c>
       <c r="K7" t="n">
-        <v>-0.431</v>
+        <v>-0.6568000000000001</v>
       </c>
       <c r="L7" t="n">
-        <v>0.5396</v>
+        <v>-0.6752</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0814</v>
+        <v>-0.9349</v>
       </c>
       <c r="N7" t="n">
-        <v>-0.7758</v>
+        <v>-0.5798</v>
       </c>
       <c r="O7" t="n">
-        <v>0.8572</v>
+        <v>-0.3551</v>
       </c>
       <c r="P7" t="n">
-        <v>-0.4162</v>
+        <v>0.4162</v>
       </c>
       <c r="Q7" t="n">
-        <v>-1.0406</v>
+        <v>0</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6244</v>
+        <v>0.4162</v>
       </c>
       <c r="S7" t="n">
-        <v>0.7078</v>
+        <v>0.1204</v>
       </c>
       <c r="T7" t="n">
-        <v>1.1802</v>
+        <v>0.1615</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.4723</v>
+        <v>-0.0411</v>
       </c>
       <c r="V7" t="n">
-        <v>-1.8751</v>
+        <v>0</v>
       </c>
       <c r="W7" t="n">
-        <v>-0.7076</v>
+        <v>0</v>
       </c>
       <c r="X7" t="n">
-        <v>-1.1675</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.5032</v>
+        <v>-1.8055</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.2593</v>
+        <v>-0.4737</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2438</v>
+        <v>-1.3319</v>
       </c>
       <c r="G8" t="n">
         <v>0.4307</v>
@@ -1078,13 +1078,13 @@
         <v>0.6244</v>
       </c>
       <c r="S8" t="n">
-        <v>0.3575</v>
+        <v>0.0551</v>
       </c>
       <c r="T8" t="n">
-        <v>0.1272</v>
+        <v>-0.0871</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2303</v>
+        <v>0.1423</v>
       </c>
       <c r="V8" t="n">
         <v>-1.8751</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>G. FERNANDEZ DIAZ</t>
+          <t>A. HERRERA DOMINGUEZ</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.0914</v>
+        <v>-1.8669</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.3848</v>
+        <v>-3.5782</v>
       </c>
       <c r="F9" t="n">
-        <v>-0.7066</v>
+        <v>1.7113</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.2669</v>
+        <v>-0.4116</v>
       </c>
       <c r="H9" t="n">
-        <v>-1.2366</v>
+        <v>-1.437</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.0303</v>
+        <v>1.0254</v>
       </c>
       <c r="J9" t="n">
-        <v>-1.332</v>
+        <v>0.005</v>
       </c>
       <c r="K9" t="n">
-        <v>-0.6568000000000001</v>
+        <v>-0.6612</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.6752</v>
+        <v>0.6662</v>
       </c>
       <c r="M9" t="n">
-        <v>-0.9349</v>
+        <v>-0.4166</v>
       </c>
       <c r="N9" t="n">
-        <v>-0.5798</v>
+        <v>-0.7758</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.3551</v>
+        <v>0.3592</v>
       </c>
       <c r="P9" t="n">
-        <v>0.4162</v>
+        <v>-1.0406</v>
       </c>
       <c r="Q9" t="n">
-        <v>0</v>
+        <v>-3.1218</v>
       </c>
       <c r="R9" t="n">
-        <v>0.4162</v>
+        <v>2.0812</v>
       </c>
       <c r="S9" t="n">
-        <v>-0.2407</v>
+        <v>-0.1848</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0529</v>
+        <v>-0.4615</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.1879</v>
+        <v>0.2767</v>
       </c>
       <c r="V9" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
       <c r="W9" t="n">
         <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>0</v>
+        <v>-0.23</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>A. MARIN ORTEGA</t>
+          <t>Z. WILLIAMS</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,73 +1189,73 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-2.1448</v>
+        <v>-1.9483</v>
       </c>
       <c r="E10" t="n">
-        <v>-1.3569</v>
+        <v>-1.1023</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.7879</v>
+        <v>-0.846</v>
       </c>
       <c r="G10" t="n">
-        <v>0.0883</v>
+        <v>0.1901</v>
       </c>
       <c r="H10" t="n">
-        <v>1.3644</v>
+        <v>-1.2068</v>
       </c>
       <c r="I10" t="n">
-        <v>-1.2761</v>
+        <v>1.3969</v>
       </c>
       <c r="J10" t="n">
-        <v>1.3458</v>
+        <v>0.1087</v>
       </c>
       <c r="K10" t="n">
-        <v>1.9484</v>
+        <v>-0.431</v>
       </c>
       <c r="L10" t="n">
-        <v>-0.6026</v>
+        <v>0.5396</v>
       </c>
       <c r="M10" t="n">
-        <v>-1.2575</v>
+        <v>0.0814</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.5839</v>
+        <v>-0.7758</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.6735</v>
+        <v>0.8572</v>
       </c>
       <c r="P10" t="n">
-        <v>-1.2487</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q10" t="n">
-        <v>-3.1218</v>
+        <v>-1.0406</v>
       </c>
       <c r="R10" t="n">
-        <v>1.8731</v>
+        <v>0.6244</v>
       </c>
       <c r="S10" t="n">
-        <v>0.5369</v>
+        <v>0.153</v>
       </c>
       <c r="T10" t="n">
-        <v>0.1891</v>
+        <v>0.5372</v>
       </c>
       <c r="U10" t="n">
-        <v>0.3478</v>
+        <v>-0.3842</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.5213</v>
+        <v>-1.8751</v>
       </c>
       <c r="W10" t="n">
-        <v>0.23</v>
+        <v>-0.7076</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.7513</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. HERRERA DOMINGUEZ</t>
+          <t>A. MARIN ORTEGA</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.2015</v>
+        <v>-2.3315</v>
       </c>
       <c r="E11" t="n">
-        <v>-4.0302</v>
+        <v>-1.6317</v>
       </c>
       <c r="F11" t="n">
-        <v>1.8287</v>
+        <v>-0.6999</v>
       </c>
       <c r="G11" t="n">
-        <v>-0.4116</v>
+        <v>0.0883</v>
       </c>
       <c r="H11" t="n">
-        <v>-1.437</v>
+        <v>1.3644</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0254</v>
+        <v>-1.2761</v>
       </c>
       <c r="J11" t="n">
-        <v>0.005</v>
+        <v>1.3458</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.6612</v>
+        <v>1.9484</v>
       </c>
       <c r="L11" t="n">
-        <v>0.6662</v>
+        <v>-0.6026</v>
       </c>
       <c r="M11" t="n">
-        <v>-0.4166</v>
+        <v>-1.2575</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7758</v>
+        <v>-0.5839</v>
       </c>
       <c r="O11" t="n">
-        <v>0.3592</v>
+        <v>-0.6735</v>
       </c>
       <c r="P11" t="n">
-        <v>-1.0406</v>
+        <v>-1.2487</v>
       </c>
       <c r="Q11" t="n">
         <v>-3.1218</v>
       </c>
       <c r="R11" t="n">
-        <v>2.0812</v>
+        <v>1.8731</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.5193</v>
+        <v>0.3502</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.9134</v>
+        <v>-0.0857</v>
       </c>
       <c r="U11" t="n">
-        <v>0.3941</v>
+        <v>0.4358</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.23</v>
+        <v>-1.5213</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="X11" t="n">
-        <v>-0.23</v>
+        <v>-1.7513</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-2.9965</v>
+        <v>-2.9541</v>
       </c>
       <c r="E12" t="n">
-        <v>-1.0092</v>
+        <v>-0.8788</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.9873</v>
+        <v>-2.0754</v>
       </c>
       <c r="G12" t="n">
         <v>1.1769</v>
@@ -1390,13 +1390,13 @@
         <v>1.2487</v>
       </c>
       <c r="S12" t="n">
-        <v>0.6185</v>
+        <v>0.6609</v>
       </c>
       <c r="T12" t="n">
-        <v>0.2701</v>
+        <v>0.4005</v>
       </c>
       <c r="U12" t="n">
-        <v>0.3484</v>
+        <v>0.2604</v>
       </c>
       <c r="V12" t="n">
         <v>-2.9188</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-9.980700000000002</v>
+        <v>-8.675799999999999</v>
       </c>
       <c r="E13" t="n">
-        <v>-4.712700000000001</v>
+        <v>-3.408</v>
       </c>
       <c r="F13" t="n">
-        <v>-5.267900000000001</v>
+        <v>-5.268000000000001</v>
       </c>
       <c r="G13" t="n">
         <v>-2.4495</v>
@@ -1444,16 +1444,16 @@
         <v>7.1254</v>
       </c>
       <c r="K13" t="n">
-        <v>7.5132</v>
+        <v>7.513199999999999</v>
       </c>
       <c r="L13" t="n">
         <v>-0.3879999999999999</v>
       </c>
       <c r="M13" t="n">
-        <v>-9.5748</v>
+        <v>-9.574799999999998</v>
       </c>
       <c r="N13" t="n">
-        <v>-8.717599999999999</v>
+        <v>-8.717600000000001</v>
       </c>
       <c r="O13" t="n">
         <v>-0.8572000000000001</v>
@@ -1468,13 +1468,13 @@
         <v>12.4871</v>
       </c>
       <c r="S13" t="n">
-        <v>0.7144000000000001</v>
+        <v>2.0194</v>
       </c>
       <c r="T13" t="n">
-        <v>-1.0117</v>
+        <v>0.2931000000000001</v>
       </c>
       <c r="U13" t="n">
-        <v>1.7259</v>
+        <v>1.7261</v>
       </c>
       <c r="V13" t="n">
         <v>-3.0427</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>5.5616</v>
+        <v>6.2505</v>
       </c>
       <c r="E14" t="n">
-        <v>4.1522</v>
+        <v>4.5809</v>
       </c>
       <c r="F14" t="n">
-        <v>1.4093</v>
+        <v>1.6697</v>
       </c>
       <c r="G14" t="n">
         <v>3.1919</v>
@@ -1546,13 +1546,13 @@
         <v>1.6649</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.7542</v>
+        <v>-0.06519999999999999</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.5872000000000001</v>
+        <v>-0.1586</v>
       </c>
       <c r="U14" t="n">
-        <v>-0.167</v>
+        <v>0.09329999999999999</v>
       </c>
       <c r="V14" t="n">
         <v>1.8751</v>
@@ -1567,7 +1567,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>L. DIBBA</t>
+          <t>J. FRANCH DE PABLO</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1579,64 +1579,64 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>3.8521</v>
+        <v>4.2395</v>
       </c>
       <c r="E15" t="n">
-        <v>2.1017</v>
+        <v>2.0004</v>
       </c>
       <c r="F15" t="n">
-        <v>1.7503</v>
+        <v>2.239</v>
       </c>
       <c r="G15" t="n">
-        <v>1.8884</v>
+        <v>4.7495</v>
       </c>
       <c r="H15" t="n">
-        <v>1.2688</v>
+        <v>-0.1001</v>
       </c>
       <c r="I15" t="n">
-        <v>0.6197</v>
+        <v>4.8496</v>
       </c>
       <c r="J15" t="n">
-        <v>1.7294</v>
+        <v>4.6517</v>
       </c>
       <c r="K15" t="n">
-        <v>1.6118</v>
+        <v>0.341</v>
       </c>
       <c r="L15" t="n">
-        <v>0.1176</v>
+        <v>4.3107</v>
       </c>
       <c r="M15" t="n">
-        <v>0.1591</v>
+        <v>0.0978</v>
       </c>
       <c r="N15" t="n">
-        <v>-0.3431</v>
+        <v>-0.4411</v>
       </c>
       <c r="O15" t="n">
-        <v>0.5021</v>
+        <v>0.5389</v>
       </c>
       <c r="P15" t="n">
-        <v>1.2487</v>
+        <v>0</v>
       </c>
       <c r="Q15" t="n">
-        <v>-0.2081</v>
+        <v>-2.2893</v>
       </c>
       <c r="R15" t="n">
-        <v>1.4568</v>
+        <v>2.2893</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1311</v>
+        <v>-0.74</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.0033</v>
+        <v>-0.5919</v>
       </c>
       <c r="U15" t="n">
-        <v>0.1344</v>
+        <v>-0.148</v>
       </c>
       <c r="V15" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="W15" t="n">
-        <v>0.5838</v>
+        <v>0.23</v>
       </c>
       <c r="X15" t="n">
         <v>0</v>
@@ -1645,7 +1645,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>J. FRANCH DE PABLO</t>
+          <t>L. DIBBA</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1657,64 +1657,64 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.8299</v>
+        <v>3.7116</v>
       </c>
       <c r="E16" t="n">
-        <v>1.6789</v>
+        <v>1.9946</v>
       </c>
       <c r="F16" t="n">
-        <v>2.151</v>
+        <v>1.7171</v>
       </c>
       <c r="G16" t="n">
-        <v>4.7495</v>
+        <v>1.8884</v>
       </c>
       <c r="H16" t="n">
-        <v>-0.1001</v>
+        <v>1.2688</v>
       </c>
       <c r="I16" t="n">
-        <v>4.8496</v>
+        <v>0.6197</v>
       </c>
       <c r="J16" t="n">
-        <v>4.6517</v>
+        <v>1.7294</v>
       </c>
       <c r="K16" t="n">
-        <v>0.341</v>
+        <v>1.6118</v>
       </c>
       <c r="L16" t="n">
-        <v>4.3107</v>
+        <v>0.1176</v>
       </c>
       <c r="M16" t="n">
-        <v>0.0978</v>
+        <v>0.1591</v>
       </c>
       <c r="N16" t="n">
-        <v>-0.4411</v>
+        <v>-0.3431</v>
       </c>
       <c r="O16" t="n">
-        <v>0.5389</v>
+        <v>0.5021</v>
       </c>
       <c r="P16" t="n">
-        <v>0</v>
+        <v>1.2487</v>
       </c>
       <c r="Q16" t="n">
-        <v>-2.2893</v>
+        <v>-0.2081</v>
       </c>
       <c r="R16" t="n">
-        <v>2.2893</v>
+        <v>1.4568</v>
       </c>
       <c r="S16" t="n">
-        <v>-1.1495</v>
+        <v>-0.009299999999999999</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.9134</v>
+        <v>-0.1105</v>
       </c>
       <c r="U16" t="n">
-        <v>-0.2361</v>
+        <v>0.1012</v>
       </c>
       <c r="V16" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="W16" t="n">
-        <v>0.23</v>
+        <v>0.5838</v>
       </c>
       <c r="X16" t="n">
         <v>0</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>3.8119</v>
+        <v>3.577</v>
       </c>
       <c r="E17" t="n">
         <v>2.2457</v>
       </c>
       <c r="F17" t="n">
-        <v>1.5663</v>
+        <v>1.3314</v>
       </c>
       <c r="G17" t="n">
         <v>2.456</v>
@@ -1780,13 +1780,13 @@
         <v>2.0812</v>
       </c>
       <c r="S17" t="n">
-        <v>-0.0385</v>
+        <v>-0.2734</v>
       </c>
       <c r="T17" t="n">
         <v>-0.5252</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4868</v>
+        <v>0.2519</v>
       </c>
       <c r="V17" t="n">
         <v>0.3538</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>2.1144</v>
+        <v>2.154</v>
       </c>
       <c r="E18" t="n">
-        <v>1.1535</v>
+        <v>1.0463</v>
       </c>
       <c r="F18" t="n">
-        <v>0.9609</v>
+        <v>1.1077</v>
       </c>
       <c r="G18" t="n">
         <v>-2.6074</v>
@@ -1858,13 +1858,13 @@
         <v>2.0812</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.0483</v>
+        <v>-0.008699999999999999</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.1338</v>
+        <v>-0.2409</v>
       </c>
       <c r="U18" t="n">
-        <v>0.08550000000000001</v>
+        <v>0.2323</v>
       </c>
       <c r="V18" t="n">
         <v>2.6889</v>
@@ -1879,7 +1879,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>M. JANKOVIC</t>
+          <t>M. BILALOVIC</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-0.063</v>
+        <v>-0.0398</v>
       </c>
       <c r="E19" t="n">
-        <v>-0.1619</v>
+        <v>-0.442</v>
       </c>
       <c r="F19" t="n">
-        <v>0.0989</v>
+        <v>0.4022</v>
       </c>
       <c r="G19" t="n">
-        <v>0.8267</v>
+        <v>-0.8777</v>
       </c>
       <c r="H19" t="n">
-        <v>0.0895</v>
+        <v>0.0832</v>
       </c>
       <c r="I19" t="n">
-        <v>0.7372</v>
+        <v>-0.9609</v>
       </c>
       <c r="J19" t="n">
-        <v>1.0595</v>
+        <v>-0.3918</v>
       </c>
       <c r="K19" t="n">
-        <v>0.4325</v>
+        <v>0.9978</v>
       </c>
       <c r="L19" t="n">
-        <v>0.627</v>
+        <v>-1.3896</v>
       </c>
       <c r="M19" t="n">
-        <v>-0.2328</v>
+        <v>-0.4859</v>
       </c>
       <c r="N19" t="n">
-        <v>-0.3431</v>
+        <v>-0.9145</v>
       </c>
       <c r="O19" t="n">
-        <v>0.1102</v>
+        <v>0.4286</v>
       </c>
       <c r="P19" t="n">
-        <v>-2.0812</v>
+        <v>-0.4162</v>
       </c>
       <c r="Q19" t="n">
-        <v>-3.3299</v>
+        <v>-1.0406</v>
       </c>
       <c r="R19" t="n">
-        <v>1.2487</v>
+        <v>0.6244</v>
       </c>
       <c r="S19" t="n">
-        <v>0.3778</v>
+        <v>-0.2672</v>
       </c>
       <c r="T19" t="n">
-        <v>0.1272</v>
+        <v>-0.1771</v>
       </c>
       <c r="U19" t="n">
-        <v>0.2506</v>
+        <v>-0.09</v>
       </c>
       <c r="V19" t="n">
-        <v>0.8137</v>
+        <v>1.5213</v>
       </c>
       <c r="W19" t="n">
-        <v>1.9813</v>
+        <v>1.1675</v>
       </c>
       <c r="X19" t="n">
-        <v>-1.1675</v>
+        <v>0.3538</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>M. BILALOVIC</t>
+          <t>M. JANKOVIC</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-0.3715</v>
+        <v>-0.1114</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.6563</v>
+        <v>-0.2691</v>
       </c>
       <c r="F20" t="n">
-        <v>0.2848</v>
+        <v>0.1576</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8777</v>
+        <v>0.8267</v>
       </c>
       <c r="H20" t="n">
-        <v>0.0832</v>
+        <v>0.0895</v>
       </c>
       <c r="I20" t="n">
-        <v>-0.9609</v>
+        <v>0.7372</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.3918</v>
+        <v>1.0595</v>
       </c>
       <c r="K20" t="n">
-        <v>0.9978</v>
+        <v>0.4325</v>
       </c>
       <c r="L20" t="n">
-        <v>-1.3896</v>
+        <v>0.627</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.4859</v>
+        <v>-0.2328</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.9145</v>
+        <v>-0.3431</v>
       </c>
       <c r="O20" t="n">
-        <v>0.4286</v>
+        <v>0.1102</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.4162</v>
+        <v>-2.0812</v>
       </c>
       <c r="Q20" t="n">
-        <v>-1.0406</v>
+        <v>-3.3299</v>
       </c>
       <c r="R20" t="n">
-        <v>0.6244</v>
+        <v>1.2487</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.5989</v>
+        <v>0.3293</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.3915</v>
+        <v>0.02</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.2075</v>
+        <v>0.3093</v>
       </c>
       <c r="V20" t="n">
-        <v>1.5213</v>
+        <v>0.8137</v>
       </c>
       <c r="W20" t="n">
-        <v>1.1675</v>
+        <v>1.9813</v>
       </c>
       <c r="X20" t="n">
-        <v>0.3538</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-0.9212</v>
+        <v>-1.1776</v>
       </c>
       <c r="E21" t="n">
-        <v>-0.0553</v>
+        <v>-0.4839</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.8659</v>
+        <v>-0.6937</v>
       </c>
       <c r="G21" t="n">
         <v>-0.4413</v>
@@ -2092,13 +2092,13 @@
         <v>2.2893</v>
       </c>
       <c r="S21" t="n">
-        <v>0.4358</v>
+        <v>0.1794</v>
       </c>
       <c r="T21" t="n">
-        <v>0.3849</v>
+        <v>-0.0438</v>
       </c>
       <c r="U21" t="n">
-        <v>0.051</v>
+        <v>0.2232</v>
       </c>
       <c r="V21" t="n">
         <v>-0.7076</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>A. LATORRE SANCHEZ</t>
+          <t>N. DEDOVIC</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-1.5574</v>
+        <v>-2.5969</v>
       </c>
       <c r="E22" t="n">
-        <v>0.5034</v>
+        <v>-3.26</v>
       </c>
       <c r="F22" t="n">
-        <v>-2.0608</v>
+        <v>0.6631</v>
       </c>
       <c r="G22" t="n">
-        <v>-1.7627</v>
+        <v>-2.1525</v>
       </c>
       <c r="H22" t="n">
-        <v>-2.0876</v>
+        <v>0.9638</v>
       </c>
       <c r="I22" t="n">
-        <v>0.3249</v>
+        <v>-3.1163</v>
       </c>
       <c r="J22" t="n">
-        <v>-1.1829</v>
+        <v>-1.3604</v>
       </c>
       <c r="K22" t="n">
-        <v>-1.2221</v>
+        <v>1.262</v>
       </c>
       <c r="L22" t="n">
-        <v>0.0392</v>
+        <v>-2.6224</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.5798</v>
+        <v>-0.7921</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.8655</v>
+        <v>-0.2982</v>
       </c>
       <c r="O22" t="n">
-        <v>0.2857</v>
+        <v>-0.4939</v>
       </c>
       <c r="P22" t="n">
-        <v>0.6244</v>
+        <v>0.8325</v>
       </c>
       <c r="Q22" t="n">
+        <v>-1.4568</v>
+      </c>
+      <c r="R22" t="n">
+        <v>2.2893</v>
+      </c>
+      <c r="S22" t="n">
+        <v>-0.1094</v>
+      </c>
+      <c r="T22" t="n">
+        <v>-0.4429</v>
+      </c>
+      <c r="U22" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="V22" t="n">
+        <v>-1.1675</v>
+      </c>
+      <c r="W22" t="n">
         <v>0</v>
       </c>
-      <c r="R22" t="n">
-        <v>0.6244</v>
-      </c>
-      <c r="S22" t="n">
-        <v>1.3322</v>
-      </c>
-      <c r="T22" t="n">
-        <v>1.1025</v>
-      </c>
-      <c r="U22" t="n">
-        <v>0.2297</v>
-      </c>
-      <c r="V22" t="n">
-        <v>-1.7513</v>
-      </c>
-      <c r="W22" t="n">
-        <v>0.5838</v>
-      </c>
       <c r="X22" t="n">
-        <v>-2.3351</v>
+        <v>-1.1675</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>R. SANTOS JIMENEZ</t>
+          <t>A. LATORRE SANCHEZ</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,73 +2203,73 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.0297</v>
+        <v>-2.6202</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.8982</v>
+        <v>-0.3539</v>
       </c>
       <c r="F23" t="n">
-        <v>-1.1316</v>
+        <v>-2.2663</v>
       </c>
       <c r="G23" t="n">
-        <v>-2.8216</v>
+        <v>-1.7627</v>
       </c>
       <c r="H23" t="n">
-        <v>-2.077</v>
+        <v>-2.0876</v>
       </c>
       <c r="I23" t="n">
-        <v>-0.7446</v>
+        <v>0.3249</v>
       </c>
       <c r="J23" t="n">
-        <v>-1.8825</v>
+        <v>-1.1829</v>
       </c>
       <c r="K23" t="n">
-        <v>-1.2073</v>
+        <v>-1.2221</v>
       </c>
       <c r="L23" t="n">
-        <v>-0.6752</v>
+        <v>0.0392</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.9391</v>
+        <v>-0.5798</v>
       </c>
       <c r="N23" t="n">
-        <v>-0.8697</v>
+        <v>-0.8655</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.0694</v>
+        <v>0.2857</v>
       </c>
       <c r="P23" t="n">
-        <v>0.8325</v>
+        <v>0.6244</v>
       </c>
       <c r="Q23" t="n">
-        <v>-0.2081</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.0406</v>
+        <v>0.6244</v>
       </c>
       <c r="S23" t="n">
-        <v>0.3569</v>
+        <v>0.2694</v>
       </c>
       <c r="T23" t="n">
-        <v>0.1924</v>
+        <v>0.2453</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1644</v>
+        <v>0.0242</v>
       </c>
       <c r="V23" t="n">
-        <v>-1.3975</v>
+        <v>-1.7513</v>
       </c>
       <c r="W23" t="n">
-        <v>0</v>
+        <v>0.5838</v>
       </c>
       <c r="X23" t="n">
-        <v>-1.3975</v>
+        <v>-2.3351</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>N. DEDOVIC</t>
+          <t>R. SANTOS JIMENEZ</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -2281,67 +2281,67 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-3.2462</v>
+        <v>-2.6916</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.7958</v>
+        <v>-1.791</v>
       </c>
       <c r="F24" t="n">
-        <v>0.5496</v>
+        <v>-0.9006</v>
       </c>
       <c r="G24" t="n">
-        <v>-2.1525</v>
+        <v>-2.8216</v>
       </c>
       <c r="H24" t="n">
-        <v>0.9638</v>
+        <v>-2.077</v>
       </c>
       <c r="I24" t="n">
-        <v>-3.1163</v>
+        <v>-0.7446</v>
       </c>
       <c r="J24" t="n">
-        <v>-1.3604</v>
+        <v>-1.8825</v>
       </c>
       <c r="K24" t="n">
-        <v>1.262</v>
+        <v>-1.2073</v>
       </c>
       <c r="L24" t="n">
-        <v>-2.6224</v>
+        <v>-0.6752</v>
       </c>
       <c r="M24" t="n">
-        <v>-0.7921</v>
+        <v>-0.9391</v>
       </c>
       <c r="N24" t="n">
-        <v>-0.2982</v>
+        <v>-0.8697</v>
       </c>
       <c r="O24" t="n">
-        <v>-0.4939</v>
+        <v>-0.0694</v>
       </c>
       <c r="P24" t="n">
         <v>0.8325</v>
       </c>
       <c r="Q24" t="n">
-        <v>-1.4568</v>
+        <v>-0.2081</v>
       </c>
       <c r="R24" t="n">
-        <v>2.2893</v>
+        <v>1.0406</v>
       </c>
       <c r="S24" t="n">
-        <v>-0.7587</v>
+        <v>0.695</v>
       </c>
       <c r="T24" t="n">
-        <v>-0.9786</v>
+        <v>0.2996</v>
       </c>
       <c r="U24" t="n">
-        <v>0.2199</v>
+        <v>0.3954</v>
       </c>
       <c r="V24" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
       <c r="W24" t="n">
         <v>0</v>
       </c>
       <c r="X24" t="n">
-        <v>-1.1675</v>
+        <v>-1.3975</v>
       </c>
     </row>
     <row r="25">
@@ -2359,16 +2359,16 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>9.980900000000002</v>
+        <v>10.69509999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>5.267899999999997</v>
+        <v>5.268000000000001</v>
       </c>
       <c r="F25" t="n">
-        <v>4.712800000000001</v>
+        <v>5.427199999999999</v>
       </c>
       <c r="G25" t="n">
-        <v>2.449300000000002</v>
+        <v>2.4493</v>
       </c>
       <c r="H25" t="n">
         <v>1.2045</v>
@@ -2386,13 +2386,13 @@
         <v>0.8569999999999993</v>
       </c>
       <c r="M25" t="n">
-        <v>-7.1252</v>
+        <v>-7.125199999999999</v>
       </c>
       <c r="N25" t="n">
-        <v>-7.513199999999999</v>
+        <v>-7.5132</v>
       </c>
       <c r="O25" t="n">
-        <v>0.3879</v>
+        <v>0.3879000000000001</v>
       </c>
       <c r="P25" t="n">
         <v>5.203099999999999</v>
@@ -2404,19 +2404,19 @@
         <v>17.6901</v>
       </c>
       <c r="S25" t="n">
-        <v>-0.7142999999999998</v>
+        <v>-9.999999999998899e-05</v>
       </c>
       <c r="T25" t="n">
         <v>-1.726</v>
       </c>
       <c r="U25" t="n">
-        <v>1.0117</v>
+        <v>1.7262</v>
       </c>
       <c r="V25" t="n">
-        <v>3.0427</v>
+        <v>3.042699999999999</v>
       </c>
       <c r="W25" t="n">
-        <v>9.9064</v>
+        <v>9.906400000000001</v>
       </c>
       <c r="X25" t="n">
         <v>-6.8636</v>
